--- a/aq_files/0089.xlsx
+++ b/aq_files/0089.xlsx
@@ -1,98 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dataset" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
-  <si>
-    <t>Two variables increase together consistently. What type of covariance do they have?</t>
-  </si>
-  <si>
-    <t>If covariance between X and Y is negative, what does it indicate about their relationship?</t>
-  </si>
-  <si>
-    <t>A dataset shows covariance = 0. Does this always mean no relationship? Explain.</t>
-  </si>
-  <si>
-    <t>Two variables have a correlation coefficient of +0.9. What does this imply?</t>
-  </si>
-  <si>
-    <t>A correlation of −0.8 between two variables suggests what kind of relationship?</t>
-  </si>
-  <si>
-    <t>If correlation coefficient is 0, what can be said about the linear relationship?</t>
-  </si>
-  <si>
-    <t>A dataset shows strong positive correlation. How will the scatter plot appear?</t>
-  </si>
-  <si>
-    <t>If covariance is very large, can we directly interpret its strength? Why or why not?</t>
-  </si>
-  <si>
-    <t>Why is correlation preferred over covariance for comparing relationships?</t>
-  </si>
-  <si>
-    <t>A dataset has correlation coefficient r = 1. What does this indicate?</t>
-  </si>
-  <si>
-    <t>If all values of one variable increase while the other decreases proportionally, what is the correlation?</t>
-  </si>
-  <si>
-    <t>A researcher standardizes variables before analysis. How does this affect covariance and correlation?</t>
-  </si>
-  <si>
-    <t>If the units of measurement change (e.g., meters to centimeters), what happens to covariance?</t>
-  </si>
-  <si>
-    <t>Does correlation change if units change? Explain.</t>
-  </si>
-  <si>
-    <t>A dataset shows a curved relationship between variables. Will Pearson correlation capture it effectively?</t>
-  </si>
-  <si>
-    <t>When should Spearman correlation be used instead of Pearson?</t>
-  </si>
-  <si>
-    <t>A correlation matrix shows high values between multiple variables. What issue might arise?</t>
-  </si>
-  <si>
-    <t>If correlation between two variables is strong, does it imply causation? Why?</t>
-  </si>
-  <si>
-    <t>A dataset contains outliers. How might they affect correlation?</t>
-  </si>
-  <si>
-    <t>A company analyzes sales and advertising spend and finds r = 0.7. How should this be interpreted?</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="10.0"/>
+      <name val="Arial"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <sz val="10"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Arial"/>
       <color theme="1"/>
-      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
@@ -102,29 +39,86 @@
     <border/>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -322,113 +316,963 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B51"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Row_ID,Order_ID,Order_Date_Text,Order_Date_Time,Order_Year_Text,Order_Month_Text,Sales_Text,Quantity_Text,Discount_Text,Profit_Text,Unit_Price_Text,Shipping_Cost_Text,Tax_Text,Region_Code,Product_Code,Status_Flag,Return_Flag,Price_Range,Weight_kg,Date_Recorded,Time_Recorded,Notes</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>1,ORD-1001,2024-01-05,2024-01-05 14:30:00,2024,January,1,299.99,1,5%,389.99,1,299.99,15.00,78.00,NW,ELEC-001,Active,N,High,2.5,2024-01-05,14:30:00,Standard order</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>2,ORD-1002,2024-01-05,2024-01-05 14:35:00,2024,January,79.99,3,10%,23.99,79.99,8.50,4.80,NW,ELEC-002,Active,N,Medium,0.2,2024-01-05,14:35:00,Accessory</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>3,ORD-1003,2024-01-06,2024-01-06 09:15:00,2024,January,89.99,2,0%,26.99,44.99,12.00,5.40,SW,CLOTH-001,Active,N,Medium,0.8,2024-01-06,09:15:00,First order</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>4,ORD-1004,2024-01-06,2024-01-06 10:45:00,2024,January,299.99,1,15%,89.99,299.99,18.00,18.00,SW,ELEC-003,Active,N,High,5.5,2024-01-06,10:45:00,Monitor</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>5,ORD-1005,2024-01-07,2024-01-07 11:20:00,2024,January,399.99,2,5%,119.99,199.99,22.00,24.00,NE,FURN-001,Active,N,High,12.0,2024-01-07,11:20:00,Heavy item</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>6,ORD-1006,2024-01-07,2024-01-07 13:00:00,2024,January,89.99,2,10%,26.99,44.99,10.00,5.40,NE,ELEC-004,Delayed,N,Medium,1.2,2024-01-07,13:00:00,Keyboard</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>7,ORD-1007,2024-01-08,2024-01-08 08:45:00,2024,January,199.99,1,20%,59.99,199.99,15.00,12.00,WC,CLOTH-002,Active,N,High,1.5,2024-01-08,08:45:00,Leather</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>8,ORD-1008,2024-01-08,2024-01-08 09:30:00,2024,January,499.99,1,5%,149.99,499.99,20.00,30.00,WC,ELEC-005,Active,N,High,1.0,2024-01-08,09:30:00,Tablet</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>9,ORD-1009,2024-01-09,2024-01-09 10:15:00,2024,January,79.99,2,0%,23.99,39.99,12.00,4.80,NW,FURN-002,Active,N,Medium,3.2,2024-01-09,10:15:00,Lamp</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>10,ORD-1010,2024-01-09,2024-01-09 14:20:00,2024,January,69.99,1,10%,20.99,69.99,10.00,4.20,NW,CLOTH-003,Returned,Y,Medium,0.7,2024-01-09,14:20:00,Returned</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>11,ORD-1011,2024-01-10,2024-01-10 11:00:00,2024,January,1,299.99,1,15%,389.99,1,299.99,25.00,78.00,SW,ELEC-006,Active,N,High,3.0,2024-01-10,11:00:00,Gaming</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12,ORD-1012,2024-01-10,2024-01-10 15:30:00,2024,January,149.99,2,5%,44.99,74.99,12.00,9.00,NE,ELEC-007,Active,N,Medium,0.4,2024-01-10,15:30:00,Audio</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>13,ORD-1013,2024-01-11,2024-01-11 09:45:00,2024,January,189.99,1,20%,56.99,189.99,15.00,11.40,WC,CLOTH-004,Active,N,High,1.3,2024-01-11,09:45:00,Coat</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>14,ORD-1014,2024-01-11,2024-01-11 12:15:00,2024,January,159.99,1,10%,47.99,159.99,18.00,9.60,NW,FURN-003,Active,N,High,8.0,2024-01-11,12:15:00,Bookshelf</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>15,ORD-1015,2024-01-12,2024-01-12 10:00:00,2024,January,699.99,2,5%,209.99,349.99,12.00,42.00,SW,ELEC-008,Active,N,High,0.5,2024-01-12,10:00:00,Phone</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>16,ORD-1016,2024-01-12,2024-01-12 13:45:00,2024,January,59.99,3,0%,17.99,20.00,10.00,3.60,NE,CLOTH-005,Active,N,Low,0.3,2024-01-12,13:45:00,Shirt</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>17,ORD-1017,2024-01-13,2024-01-13 08:30:00,2024,January,99.99,1,10%,29.99,99.99,8.50,6.00,WC,ELEC-009,Active,N,Medium,0.2,2024-01-13,08:30:00,SSD</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>18,ORD-1018,2024-01-13,2024-01-13 16:20:00,2024,January,49.99,2,5%,14.99,25.00,12.00,3.00,NW,CLOTH-006,Returned,Y,Low,0.5,2024-01-13,16:20:00,Hoodie</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>19,ORD-1019,2024-01-14,2024-01-14 11:30:00,2024,January,349.99,1,15%,104.99,349.99,25.00,21.00,SW,FURN-004,Active,N,High,15.0,2024-01-14,11:30:00,Desk</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>20,ORD-1020,2024-01-14,2024-01-14 14:15:00,2024,January,79.99,2,10%,23.99,39.99,8.50,4.80,NE,ELEC-010,Active,N,Medium,0.3,2024-01-14,14:15:00,Webcam</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>21,ORD-1021,2024-02-01,2024-02-01 09:00:00,2024,February,129.99,1,0%,38.99,129.99,10.00,7.80,WC,ELEC-011,Active,N,Medium,0.6,2024-02-01,09:00:00,Dock</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>22,ORD-1022,2024-02-01,2024-02-01 10:45:00,2024,February,179.99,1,5%,53.99,179.99,15.00,10.80,NW,CLOTH-007,Active,N,High,1.2,2024-02-01,10:45:00,Parka</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>23,ORD-1023,2024-02-02,2024-02-02 13:30:00,2024,February,449.99,1,10%,134.99,449.99,22.00,27.00,SW,FURN-005,Active,N,High,20.0,2024-02-02,13:30:00,Desk</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>24,ORD-1024,2024-02-02,2024-02-02 15:20:00,2024,February,39.99,3,0%,11.99,13.33,8.50,2.40,NE,ELEC-012,Active,N,Low,0.1,2024-02-02,15:20:00,Hub</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>25,ORD-1025,2024-02-03,2024-02-03 08:15:00,2024,February,149.99,1,15%,44.99,149.99,12.00,9.00,WC,CLOTH-008,Active,N,Medium,0.9,2024-02-03,08:15:00,Blazer</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>26,ORD-1026,2024-02-03,2024-02-03 11:45:00,2024,February,59.99,2,10%,17.99,29.99,8.50,3.60,NW,ELEC-013,Returned,Y,Low,0.2,2024-02-03,11:45:00,Mouse</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>27,ORD-1027,2024-02-04,2024-02-04 09:30:00,2024,February,199.99,1,5%,59.99,199.99,18.00,12.00,SW,ELEC-014,Active,N,High,8.0,2024-02-04,09:30:00,Printer</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>28,ORD-1028,2024-02-04,2024-02-04 14:00:00,2024,February,279.99,1,20%,83.99,279.99,22.00,16.80,NE,FURN-006,Active,N,High,10.0,2024-02-04,14:00:00,Chair</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>29,ORD-1029,2024-02-05,2024-02-05 10:15:00,2024,February,49.99,4,0%,14.99,12.50,8.50,3.00,WC,ELEC-015,Active,N,Low,0.4,2024-02-05,10:15:00,Power Bank</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>30,ORD-1030,2024-02-05,2024-02-05 12:30:00,2024,February,24.99,5,10%,7.49,5.00,8.50,1.50,NW,CLOTH-009,Active,N,Low,0.1,2024-02-05,12:30:00,Scarf</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>31,ORD-1031,2024-02-06,2024-02-06 13:45:00,2024,February,119.99,1,5%,35.99,119.99,12.00,7.20,SW,ELEC-016,Active,N,Medium,0.5,2024-02-06,13:45:00,Headset</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>32,ORD-1032,2024-02-06,2024-02-06 15:30:00,2024,February,69.99,2,10%,20.99,34.99,15.00,4.20,NE,FURN-007,Active,N,Medium,5.0,2024-02-06,15:30:00,Night Stand</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>33,ORD-1033,2024-02-07,2024-02-07 09:20:00,2024,February,109.99,1,15%,32.99,109.99,10.00,6.60,WC,CLOTH-010,Active,N,Medium,0.6,2024-02-07,09:20:00,Shoes</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>34,ORD-1034,2024-02-07,2024-02-07 11:00:00,2024,February,199.99,1,5%,59.99,199.99,12.00,12.00,NW,ELEC-017,Active,N,High,0.3,2024-02-07,11:00:00,Watch</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>35,ORD-1035,2024-02-08,2024-02-08 14:15:00,2024,February,79.99,2,10%,23.99,39.99,10.00,4.80,SW,ELEC-018,Active,N,Medium,0.5,2024-02-08,14:15:00,Speaker</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>36,ORD-1036,2024-02-08,2024-02-08 16:45:00,2024,February,99.99,1,0%,29.99,99.99,12.00,6.00,NE,CLOTH-011,Returned,Y,Medium,0.4,2024-02-08,16:45:00,Sweater</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>37,ORD-1037,2024-02-09,2024-02-09 10:30:00,2024,February,129.99,1,5%,38.99,129.99,18.00,7.80,WC,FURN-008,Active,N,Medium,8.0,2024-02-09,10:30:00,Bookshelf</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>38,ORD-1038,2024-02-09,2024-02-09 12:00:00,2024,February,99.99,1,10%,29.99,99.99,10.00,6.00,NW,ELEC-019,Active,N,Medium,0.8,2024-02-09,12:00:00,Router</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>39,ORD-1039,2024-02-10,2024-02-10 09:45:00,2024,February,44.99,3,15%,13.49,15.00,8.50,2.70,SW,CLOTH-012,Active,N,Low,0.3,2024-02-10,09:45:00,Polo</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>40,ORD-1040,2024-02-10,2024-02-10 13:15:00,2024,February,499.99,1,20%,149.99,499.99,18.00,30.00,WC,ELEC-020,Active,N,High,1.2,2024-02-10,13:15:00,GPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>41,ORD-1041,2024-03-01,2024-03-01 10:00:00,2024,March,999.99,1,5%,299.99,999.99,25.00,60.00,NW,ELEC-021,Active,N,High,8.0,2024-03-01,10:00:00,Desktop</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>42,ORD-1042,2024-03-01,2024-03-01 11:30:00,2024,March,49.99,2,0%,14.99,25.00,8.50,3.00,SW,CLOTH-013,Active,N,Low,0.3,2024-03-01,11:30:00,Yoga</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>43,ORD-1043,2024-03-02,2024-03-02 14:45:00,2024,March,249.99,1,10%,74.99,249.99,22.00,15.00,NE,FURN-009,Active,N,High,12.0,2024-03-02,14:45:00,Coffee Table</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>44,ORD-1044,2024-03-02,2024-03-02 16:20:00,2024,March,89.99,2,0%,26.99,45.00,10.00,5.40,WC,ELEC-022,Active,N,Medium,0.7,2024-03-02,16:20:00,Speaker</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>45,ORD-1045,2024-03-03,2024-03-03 08:30:00,2024,March,19.99,4,5%,5.99,5.00,8.50,1.20,NW,CLOTH-014,Active,N,Low,0.1,2024-03-03,08:30:00,Cap</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>46,ORD-1046,2024-03-03,2024-03-03 12:15:00,2024,March,349.99,1,10%,104.99,349.99,18.00,21.00,SW,ELEC-023,Active,N,High,1.5,2024-03-03,12:15:00,Drone</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>47,ORD-1047,2024-03-04,2024-03-04 09:45:00,2024,March,59.99,2,0%,17.99,30.00,12.00,3.60,NE,FURN-010,Active,N,Medium,4.0,2024-03-04,09:45:00,Mirror</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>48,ORD-1048,2024-03-04,2024-03-04 13:30:00,2024,March,49.99,2,10%,14.99,25.00,10.00,3.00,WC,CLOTH-015,Active,N,Low,0.5,2024-03-04,13:30:00,Shirt</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>49,ORD-1049,2024-03-05,2024-03-05 10:30:00,2024,March,29.99,3,5%,8.99,10.00,8.50,1.80,NW,ELEC-024,Returned,Y,Low,0.2,2024-03-05,10:30:00,Stick</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>50,ORD-1050,2024-03-05,2024-03-05 14:00:00,2024,March,29.99,4,0%,8.99,7.50,8.50,1.80,SW,CLOTH-016,Active,N,Low,0.3,2024-03-05,14:00:00,Leggings</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>Question No.</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="C1" s="0" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
+      </c>
+      <c r="D1" s="0" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="E1" s="0" t="inlineStr">
+        <is>
+          <t>Scenario/Context</t>
+        </is>
+      </c>
+      <c r="F1" s="0" t="inlineStr">
+        <is>
+          <t>Skills Tested</t>
+        </is>
+      </c>
+      <c r="G1" s="0" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+      <c r="H1" s="0" t="inlineStr">
+        <is>
+          <t>Option B</t>
+        </is>
+      </c>
+      <c r="I1" s="0" t="inlineStr">
+        <is>
+          <t>Option C</t>
+        </is>
+      </c>
+      <c r="J1" s="0" t="inlineStr">
+        <is>
+          <t>Option D</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>Changing Data Types</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D2" s="0" t="inlineStr">
+        <is>
+          <t>Load the dataset into Power Query Editor. Identify all columns with incorrect data types. List the current data type and the correct data type for each column.</t>
+        </is>
+      </c>
+      <c r="E2" s="0" t="inlineStr"/>
+      <c r="F2" s="0" t="inlineStr"/>
+      <c r="G2" s="0" t="inlineStr"/>
+      <c r="H2" s="0" t="inlineStr"/>
+      <c r="I2" s="0" t="inlineStr"/>
+      <c r="J2" s="0" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="0" t="n">
         <v>2</v>
       </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>Changing Data Types</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D3" s="0" t="inlineStr">
+        <is>
+          <t>Change 'Order_Date_Text' from Text to Date type. How many rows have invalid dates? Handle any conversion errors.</t>
+        </is>
+      </c>
+      <c r="E3" s="0" t="inlineStr"/>
+      <c r="F3" s="0" t="inlineStr"/>
+      <c r="G3" s="0" t="inlineStr"/>
+      <c r="H3" s="0" t="inlineStr"/>
+      <c r="I3" s="0" t="inlineStr"/>
+      <c r="J3" s="0" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="0" t="n">
         <v>3</v>
       </c>
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>Changing Data Types</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D4" s="0" t="inlineStr">
+        <is>
+          <t>Change 'Order_Date_Time' from Text to Date/Time type. Verify that both date and time are preserved.</t>
+        </is>
+      </c>
+      <c r="E4" s="0" t="inlineStr"/>
+      <c r="F4" s="0" t="inlineStr"/>
+      <c r="G4" s="0" t="inlineStr"/>
+      <c r="H4" s="0" t="inlineStr"/>
+      <c r="I4" s="0" t="inlineStr"/>
+      <c r="J4" s="0" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="0" t="n">
         <v>4</v>
       </c>
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t>Changing Data Types</t>
+        </is>
+      </c>
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D5" s="0" t="inlineStr">
+        <is>
+          <t>Change 'Sales_Text' from Text to Decimal Number. What is the total sales amount after conversion?</t>
+        </is>
+      </c>
+      <c r="E5" s="0" t="inlineStr"/>
+      <c r="F5" s="0" t="inlineStr"/>
+      <c r="G5" s="0" t="inlineStr"/>
+      <c r="H5" s="0" t="inlineStr"/>
+      <c r="I5" s="0" t="inlineStr"/>
+      <c r="J5" s="0" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="0" t="n">
         <v>5</v>
       </c>
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t>Changing Data Types</t>
+        </is>
+      </c>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D6" s="0" t="inlineStr">
+        <is>
+          <t>Change 'Quantity_Text' from Text to Whole Number. What is the total quantity sold after conversion?</t>
+        </is>
+      </c>
+      <c r="E6" s="0" t="inlineStr"/>
+      <c r="F6" s="0" t="inlineStr"/>
+      <c r="G6" s="0" t="inlineStr"/>
+      <c r="H6" s="0" t="inlineStr"/>
+      <c r="I6" s="0" t="inlineStr"/>
+      <c r="J6" s="0" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="0" t="n">
         <v>6</v>
       </c>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t>Changing Data Types</t>
+        </is>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D7" s="0" t="inlineStr">
+        <is>
+          <t>Change 'Discount_Text' from Text to Percentage. Remove the % symbol and convert properly.</t>
+        </is>
+      </c>
+      <c r="E7" s="0" t="inlineStr"/>
+      <c r="F7" s="0" t="inlineStr"/>
+      <c r="G7" s="0" t="inlineStr"/>
+      <c r="H7" s="0" t="inlineStr"/>
+      <c r="I7" s="0" t="inlineStr"/>
+      <c r="J7" s="0" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="0" t="n">
         <v>7</v>
       </c>
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t>Changing Data Types</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D8" s="0" t="inlineStr">
+        <is>
+          <t>Change 'Profit_Text' from Text to Decimal Number. What is the total profit?</t>
+        </is>
+      </c>
+      <c r="E8" s="0" t="inlineStr"/>
+      <c r="F8" s="0" t="inlineStr"/>
+      <c r="G8" s="0" t="inlineStr"/>
+      <c r="H8" s="0" t="inlineStr"/>
+      <c r="I8" s="0" t="inlineStr"/>
+      <c r="J8" s="0" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="0" t="n">
         <v>8</v>
       </c>
+      <c r="B9" s="0" t="inlineStr">
+        <is>
+          <t>Changing Data Types</t>
+        </is>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D9" s="0" t="inlineStr">
+        <is>
+          <t>Change 'Unit_Price_Text' from Text to Decimal Number. Then change 'Shipping_Cost_Text' and 'Tax_Text' to Decimal Number.</t>
+        </is>
+      </c>
+      <c r="E9" s="0" t="inlineStr"/>
+      <c r="F9" s="0" t="inlineStr"/>
+      <c r="G9" s="0" t="inlineStr"/>
+      <c r="H9" s="0" t="inlineStr"/>
+      <c r="I9" s="0" t="inlineStr"/>
+      <c r="J9" s="0" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="0" t="n">
         <v>9</v>
       </c>
+      <c r="B10" s="0" t="inlineStr">
+        <is>
+          <t>Changing Data Types</t>
+        </is>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D10" s="0" t="inlineStr">
+        <is>
+          <t>Change 'Order_Year_Text' from Text to Whole Number. Then change 'Order_Month_Text' to Text (for grouping).</t>
+        </is>
+      </c>
+      <c r="E10" s="0" t="inlineStr"/>
+      <c r="F10" s="0" t="inlineStr"/>
+      <c r="G10" s="0" t="inlineStr"/>
+      <c r="H10" s="0" t="inlineStr"/>
+      <c r="I10" s="0" t="inlineStr"/>
+      <c r="J10" s="0" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="0" t="n">
         <v>10</v>
       </c>
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t>Changing Data Types</t>
+        </is>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D11" s="0" t="inlineStr">
+        <is>
+          <t>Change 'Region_Code' from Text to Text (no change). Change 'Product_Code' to Text. These are dimensions.</t>
+        </is>
+      </c>
+      <c r="E11" s="0" t="inlineStr"/>
+      <c r="F11" s="0" t="inlineStr"/>
+      <c r="G11" s="0" t="inlineStr"/>
+      <c r="H11" s="0" t="inlineStr"/>
+      <c r="I11" s="0" t="inlineStr"/>
+      <c r="J11" s="0" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="0" t="n">
         <v>11</v>
       </c>
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t>Changing Data Types</t>
+        </is>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D12" s="0" t="inlineStr">
+        <is>
+          <t>Change 'Status_Flag' to Text. Then change 'Return_Flag' to True/False (Logical) type.</t>
+        </is>
+      </c>
+      <c r="E12" s="0" t="inlineStr"/>
+      <c r="F12" s="0" t="inlineStr"/>
+      <c r="G12" s="0" t="inlineStr"/>
+      <c r="H12" s="0" t="inlineStr"/>
+      <c r="I12" s="0" t="inlineStr"/>
+      <c r="J12" s="0" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="0" t="n">
         <v>12</v>
       </c>
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t>Changing Data Types</t>
+        </is>
+      </c>
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D13" s="0" t="inlineStr">
+        <is>
+          <t>Change 'Price_Range' from Text to Text (categorical). This is a dimension column for grouping.</t>
+        </is>
+      </c>
+      <c r="E13" s="0" t="inlineStr"/>
+      <c r="F13" s="0" t="inlineStr"/>
+      <c r="G13" s="0" t="inlineStr"/>
+      <c r="H13" s="0" t="inlineStr"/>
+      <c r="I13" s="0" t="inlineStr"/>
+      <c r="J13" s="0" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="0" t="n">
         <v>13</v>
       </c>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t>Changing Data Types</t>
+        </is>
+      </c>
+      <c r="C14" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D14" s="0" t="inlineStr">
+        <is>
+          <t>Change 'Weight_kg' from Text to Decimal Number. What is the average weight?</t>
+        </is>
+      </c>
+      <c r="E14" s="0" t="inlineStr"/>
+      <c r="F14" s="0" t="inlineStr"/>
+      <c r="G14" s="0" t="inlineStr"/>
+      <c r="H14" s="0" t="inlineStr"/>
+      <c r="I14" s="0" t="inlineStr"/>
+      <c r="J14" s="0" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="0" t="n">
         <v>14</v>
       </c>
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t>Changing Data Types</t>
+        </is>
+      </c>
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D15" s="0" t="inlineStr">
+        <is>
+          <t>Change 'Date_Recorded' from Text to Date. Change 'Time_Recorded' from Text to Time.</t>
+        </is>
+      </c>
+      <c r="E15" s="0" t="inlineStr"/>
+      <c r="F15" s="0" t="inlineStr"/>
+      <c r="G15" s="0" t="inlineStr"/>
+      <c r="H15" s="0" t="inlineStr"/>
+      <c r="I15" s="0" t="inlineStr"/>
+      <c r="J15" s="0" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="0" t="n">
         <v>15</v>
       </c>
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t>Changing Data Types</t>
+        </is>
+      </c>
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D16" s="0" t="inlineStr">
+        <is>
+          <t>Use 'Detect Data Type' feature on all columns. Which columns does Power BI correctly detect? Which ones need manual override?</t>
+        </is>
+      </c>
+      <c r="E16" s="0" t="inlineStr"/>
+      <c r="F16" s="0" t="inlineStr"/>
+      <c r="G16" s="0" t="inlineStr"/>
+      <c r="H16" s="0" t="inlineStr"/>
+      <c r="I16" s="0" t="inlineStr"/>
+      <c r="J16" s="0" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="0" t="n">
         <v>16</v>
       </c>
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t>Changing Data Types</t>
+        </is>
+      </c>
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D17" s="0" t="inlineStr">
+        <is>
+          <t>Change 'Sales_Text' to Decimal Number. Handle any errors by replacing errors with 0. How many errors were replaced?</t>
+        </is>
+      </c>
+      <c r="E17" s="0" t="inlineStr"/>
+      <c r="F17" s="0" t="inlineStr"/>
+      <c r="G17" s="0" t="inlineStr"/>
+      <c r="H17" s="0" t="inlineStr"/>
+      <c r="I17" s="0" t="inlineStr"/>
+      <c r="J17" s="0" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="0" t="n">
         <v>17</v>
       </c>
+      <c r="B18" s="0" t="inlineStr">
+        <is>
+          <t>Changing Data Types</t>
+        </is>
+      </c>
+      <c r="C18" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D18" s="0" t="inlineStr">
+        <is>
+          <t>Change 'Discount_Text' to Percentage using locale settings for European format (comma as decimal).</t>
+        </is>
+      </c>
+      <c r="E18" s="0" t="inlineStr"/>
+      <c r="F18" s="0" t="inlineStr"/>
+      <c r="G18" s="0" t="inlineStr"/>
+      <c r="H18" s="0" t="inlineStr"/>
+      <c r="I18" s="0" t="inlineStr"/>
+      <c r="J18" s="0" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="0" t="n">
         <v>18</v>
       </c>
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t>Changing Data Types</t>
+        </is>
+      </c>
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D19" s="0" t="inlineStr">
+        <is>
+          <t>Create a duplicate column of 'Sales_Text'. Convert one to Decimal Number and keep one as Text for display.</t>
+        </is>
+      </c>
+      <c r="E19" s="0" t="inlineStr"/>
+      <c r="F19" s="0" t="inlineStr"/>
+      <c r="G19" s="0" t="inlineStr"/>
+      <c r="H19" s="0" t="inlineStr"/>
+      <c r="I19" s="0" t="inlineStr"/>
+      <c r="J19" s="0" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="0" t="n">
         <v>19</v>
       </c>
+      <c r="B20" s="0" t="inlineStr">
+        <is>
+          <t>Changing Data Types</t>
+        </is>
+      </c>
+      <c r="C20" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D20" s="0" t="inlineStr">
+        <is>
+          <t>Change 'Order_Date_Time' to Date only. Use 'Extract Date' feature. Then change the new column to Date type.</t>
+        </is>
+      </c>
+      <c r="E20" s="0" t="inlineStr"/>
+      <c r="F20" s="0" t="inlineStr"/>
+      <c r="G20" s="0" t="inlineStr"/>
+      <c r="H20" s="0" t="inlineStr"/>
+      <c r="I20" s="0" t="inlineStr"/>
+      <c r="J20" s="0" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="0" t="inlineStr">
+        <is>
+          <t>Changing Data Types</t>
+        </is>
+      </c>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D21" s="0" t="inlineStr">
+        <is>
+          <t>Use 'Data Type' dropdown to change 'Quantity_Text' to Whole Number. Then verify in Model View that the data type is correct.</t>
+        </is>
+      </c>
+      <c r="E21" s="0" t="inlineStr"/>
+      <c r="F21" s="0" t="inlineStr"/>
+      <c r="G21" s="0" t="inlineStr"/>
+      <c r="H21" s="0" t="inlineStr"/>
+      <c r="I21" s="0" t="inlineStr"/>
+      <c r="J21" s="0" t="inlineStr"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>